--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104613_W18.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104613_W18.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.77</v>
+        <v>6.51</v>
       </c>
       <c r="E2" t="n">
-        <v>4.3237</v>
+        <v>2.9369</v>
       </c>
       <c r="F2" t="n">
-        <v>3.4463</v>
+        <v>3.5731</v>
       </c>
       <c r="G2" t="n">
-        <v>1.5523</v>
+        <v>1.5557</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2541</v>
+        <v>0.2474</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2982</v>
+        <v>1.3083</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3094</v>
+        <v>0.2891</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.4369</v>
+        <v>-0.4556</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7463</v>
+        <v>0.7447</v>
       </c>
       <c r="M2" t="n">
-        <v>1.2428</v>
+        <v>1.2666</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.703</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5518999999999999</v>
+        <v>0.5636</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R2" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S2" t="n">
-        <v>1.9831</v>
+        <v>0.733</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7512</v>
+        <v>0.4085</v>
       </c>
       <c r="U2" t="n">
-        <v>0.232</v>
+        <v>0.3245</v>
       </c>
       <c r="V2" t="n">
-        <v>5.1419</v>
+        <v>5.1318</v>
       </c>
       <c r="W2" t="n">
-        <v>4.5314</v>
+        <v>4.5157</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6105</v>
+        <v>0.6162</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6713</v>
+        <v>3.5039</v>
       </c>
       <c r="E3" t="n">
-        <v>4.7656</v>
+        <v>4.3872</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.0943</v>
+        <v>-0.8833</v>
       </c>
       <c r="G3" t="n">
-        <v>3.2879</v>
+        <v>3.2821</v>
       </c>
       <c r="H3" t="n">
-        <v>3.1732</v>
+        <v>3.1627</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1147</v>
+        <v>0.1194</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6019</v>
+        <v>3.5804</v>
       </c>
       <c r="K3" t="n">
-        <v>2.7809</v>
+        <v>2.7612</v>
       </c>
       <c r="L3" t="n">
-        <v>0.821</v>
+        <v>0.8192</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.314</v>
+        <v>-0.2982</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3923</v>
+        <v>0.4016</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.7063</v>
+        <v>-0.6998</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4761</v>
+        <v>0.3112</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6835</v>
+        <v>0.3319</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2075</v>
+        <v>-0.0207</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="4">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5309</v>
+        <v>3.4772</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4844</v>
+        <v>1.9307</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0465</v>
+        <v>1.5465</v>
       </c>
       <c r="G4" t="n">
-        <v>1.7694</v>
+        <v>1.7547</v>
       </c>
       <c r="H4" t="n">
-        <v>2.0547</v>
+        <v>2.0563</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2853</v>
+        <v>-0.3016</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2778</v>
+        <v>1.2341</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7419</v>
+        <v>1.7269</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.464</v>
+        <v>-0.4929</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4915</v>
+        <v>0.5206</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3129</v>
+        <v>0.3294</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1787</v>
+        <v>0.1912</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.2385</v>
+        <v>-0.2775</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6593</v>
+        <v>-0.1652</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5792</v>
+        <v>-0.1122</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. LUZ</t>
+          <t>C. ORTEGA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.319</v>
+        <v>2.9731</v>
       </c>
       <c r="E5" t="n">
-        <v>2.4428</v>
+        <v>-0.4756</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1237</v>
+        <v>3.4487</v>
       </c>
       <c r="G5" t="n">
-        <v>4.816</v>
+        <v>0.3853</v>
       </c>
       <c r="H5" t="n">
-        <v>2.417</v>
+        <v>0.4072</v>
       </c>
       <c r="I5" t="n">
-        <v>2.399</v>
+        <v>-0.0219</v>
       </c>
       <c r="J5" t="n">
-        <v>5.4763</v>
+        <v>-1.1118</v>
       </c>
       <c r="K5" t="n">
-        <v>2.5282</v>
+        <v>-0.5828</v>
       </c>
       <c r="L5" t="n">
-        <v>2.948</v>
+        <v>-0.529</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6603</v>
+        <v>1.4971</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1113</v>
+        <v>0.99</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.549</v>
+        <v>0.5071</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.5878</v>
+        <v>1.3658</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.722</v>
+        <v>-0.2276</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1342</v>
+        <v>1.5934</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1836</v>
+        <v>0.1326</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3115</v>
+        <v>-0.2257</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4951</v>
+        <v>0.3583</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. ORTEGA</t>
+          <t>R. LUZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0403</v>
+        <v>2.5215</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.124</v>
+        <v>2.8403</v>
       </c>
       <c r="F6" t="n">
-        <v>3.1643</v>
+        <v>-0.3188</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3633</v>
+        <v>4.8153</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3952</v>
+        <v>2.4155</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0319</v>
+        <v>2.3998</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.1037</v>
+        <v>5.4583</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5786</v>
+        <v>2.5166</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5251</v>
+        <v>2.9417</v>
       </c>
       <c r="M6" t="n">
-        <v>1.467</v>
+        <v>-0.643</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9737</v>
+        <v>-0.1011</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4932</v>
+        <v>-0.5419</v>
       </c>
       <c r="P6" t="n">
-        <v>1.361</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2268</v>
+        <v>-2.7316</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5878</v>
+        <v>1.1382</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7766999999999999</v>
+        <v>0.3891</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8861</v>
+        <v>0.1136</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1095</v>
+        <v>0.2755</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="7">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4786</v>
+        <v>2.0517</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1098</v>
+        <v>0.3667</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5884</v>
+        <v>1.685</v>
       </c>
       <c r="G7" t="n">
-        <v>4.0265</v>
+        <v>4.0105</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.3143</v>
+        <v>-3.3225</v>
       </c>
       <c r="I7" t="n">
-        <v>7.3408</v>
+        <v>7.333</v>
       </c>
       <c r="J7" t="n">
-        <v>2.9886</v>
+        <v>2.9451</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.8004</v>
+        <v>-3.8243</v>
       </c>
       <c r="L7" t="n">
-        <v>6.7889</v>
+        <v>6.7694</v>
       </c>
       <c r="M7" t="n">
-        <v>1.0379</v>
+        <v>1.0653</v>
       </c>
       <c r="N7" t="n">
-        <v>0.486</v>
+        <v>0.5018</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5518999999999999</v>
+        <v>0.5636</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6236</v>
+        <v>-0.0207</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.747</v>
+        <v>-0.2047</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1234</v>
+        <v>0.184</v>
       </c>
       <c r="V7" t="n">
-        <v>1.4783</v>
+        <v>1.4764</v>
       </c>
       <c r="W7" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. OKOYE</t>
+          <t>J. MCKOY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2566</v>
+        <v>1.1757</v>
       </c>
       <c r="E8" t="n">
-        <v>2.0849</v>
+        <v>-0.3826</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8284</v>
+        <v>1.5583</v>
       </c>
       <c r="G8" t="n">
-        <v>1.068</v>
+        <v>0.2427</v>
       </c>
       <c r="H8" t="n">
-        <v>3.0778</v>
+        <v>0.3788</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.0098</v>
+        <v>-0.136</v>
       </c>
       <c r="J8" t="n">
-        <v>1.587</v>
+        <v>-0.2198</v>
       </c>
       <c r="K8" t="n">
-        <v>3.0477</v>
+        <v>-0.1519</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.4608</v>
+        <v>-0.0679</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5189</v>
+        <v>0.4625</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0301</v>
+        <v>0.5306</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.549</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.4537</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.361</v>
+        <v>0.9105</v>
       </c>
       <c r="S8" t="n">
-        <v>1.4665</v>
+        <v>0.1802</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4053</v>
+        <v>-0.1628</v>
       </c>
       <c r="U8" t="n">
-        <v>1.0613</v>
+        <v>0.343</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.1853</v>
+        <v>-0.1578</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.7317</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. MCKOY</t>
+          <t>S. OKOYE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0808</v>
+        <v>0.6728</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7321</v>
+        <v>2.0641</v>
       </c>
       <c r="F9" t="n">
-        <v>1.8129</v>
+        <v>-1.3913</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2468</v>
+        <v>1.0666</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3722</v>
+        <v>3.0761</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1254</v>
+        <v>-2.0095</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1938</v>
+        <v>1.5661</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1456</v>
+        <v>3.0337</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0481</v>
+        <v>-1.4676</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4406</v>
+        <v>-0.4995</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5178</v>
+        <v>0.0424</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0772</v>
+        <v>-0.5419</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.4553</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="S9" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.8746</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5383</v>
+        <v>0.4085</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6257</v>
+        <v>0.4661</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1607</v>
+        <v>-2.1789</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1607</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="10">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3422</v>
+        <v>-1.2567</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4009</v>
+        <v>-1.3498</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0586</v>
+        <v>0.0931</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.5699</v>
+        <v>-1.5737</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.7271</v>
+        <v>-1.7316</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.5381</v>
+        <v>-1.5448</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.5381</v>
+        <v>-1.5448</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0318</v>
+        <v>-0.0289</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1891</v>
+        <v>-0.1868</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S10" t="n">
-        <v>1.2276</v>
+        <v>0.317</v>
       </c>
       <c r="T10" t="n">
-        <v>1.364</v>
+        <v>0.4226</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1364</v>
+        <v>-0.1057</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.7487</v>
+        <v>-2.8565</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0958</v>
+        <v>-1.0374</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6529</v>
+        <v>-1.8191</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9985000000000001</v>
+        <v>1.0091</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3001</v>
+        <v>0.3042</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6984</v>
+        <v>0.7049</v>
       </c>
       <c r="J11" t="n">
-        <v>1.0697</v>
+        <v>1.0653</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8832</v>
+        <v>0.8791</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1866</v>
+        <v>0.1862</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0712</v>
+        <v>-0.0562</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5831</v>
+        <v>-0.5749</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5118</v>
+        <v>0.5187</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1101</v>
+        <v>-0.2298</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2601</v>
+        <v>-0.1906</v>
       </c>
       <c r="U11" t="n">
-        <v>0.15</v>
+        <v>-0.0392</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.9566</v>
+        <v>-2.9529</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.3948</v>
+        <v>-3.4187</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.7616</v>
+        <v>-2.0064</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6332</v>
+        <v>-1.4123</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.7797</v>
+        <v>-1.7776</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.2599</v>
+        <v>-1.2499</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5198</v>
+        <v>-0.5276999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.584</v>
+        <v>-0.603</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.6132</v>
+        <v>-0.6173</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0292</v>
+        <v>0.0142</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.1957</v>
+        <v>-1.1745</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.549</v>
+        <v>-0.5419</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="R12" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5886</v>
+        <v>0.3785</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5898</v>
+        <v>0.1901</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0012</v>
+        <v>0.1884</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="13">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>14.6618</v>
+        <v>15.354</v>
       </c>
       <c r="E13" t="n">
-        <v>8.8772</v>
+        <v>9.274100000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>5.784500000000001</v>
+        <v>6.079900000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>14.7791</v>
+        <v>14.7707</v>
       </c>
       <c r="H13" t="n">
-        <v>5.742999999999999</v>
+        <v>5.744199999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>9.036199999999999</v>
+        <v>9.026600000000002</v>
       </c>
       <c r="J13" t="n">
-        <v>12.8911</v>
+        <v>12.659</v>
       </c>
       <c r="K13" t="n">
-        <v>3.8691</v>
+        <v>3.740799999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>9.021999999999998</v>
+        <v>8.917999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>1.8879</v>
+        <v>2.1118</v>
       </c>
       <c r="N13" t="n">
-        <v>1.8736</v>
+        <v>2.0034</v>
       </c>
       <c r="O13" t="n">
-        <v>0.01429999999999965</v>
+        <v>0.1084999999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q13" t="n">
-        <v>-13.6099</v>
+        <v>-13.6578</v>
       </c>
       <c r="R13" t="n">
-        <v>11.3417</v>
+        <v>11.3817</v>
       </c>
       <c r="S13" t="n">
-        <v>2.0868</v>
+        <v>2.7882</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2119000000000003</v>
+        <v>0.9261999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>1.8751</v>
+        <v>1.862000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>0.06429999999999891</v>
+        <v>0.07139999999999991</v>
       </c>
       <c r="W13" t="n">
-        <v>9.384299999999998</v>
+        <v>9.3469</v>
       </c>
       <c r="X13" t="n">
-        <v>-9.3201</v>
+        <v>-9.275399999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>L. LABEYRIE</t>
+          <t>E. VILA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.1631</v>
+        <v>2.1712</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3251</v>
+        <v>0.2899</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1619</v>
+        <v>1.8814</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2562</v>
+        <v>0.7098</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8772</v>
+        <v>0.0974</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.621</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>1.9583</v>
+        <v>0.1924</v>
       </c>
       <c r="K14" t="n">
-        <v>1.697</v>
+        <v>0.1551</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2612</v>
+        <v>0.0372</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.702</v>
+        <v>0.5174</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.8198</v>
+        <v>-0.0578</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.8822</v>
+        <v>0.5752</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9073</v>
+        <v>0.6829</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.0415</v>
+        <v>0.6829</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2284</v>
+        <v>0.3915</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4083</v>
+        <v>0.0975</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.18</v>
+        <v>0.294</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7712</v>
+        <v>0.387</v>
       </c>
       <c r="W14" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.3214</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. VILA</t>
+          <t>L. LABEYRIE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8578</v>
+        <v>1.7961</v>
       </c>
       <c r="E15" t="n">
-        <v>0.054</v>
+        <v>1.6034</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8037</v>
+        <v>0.1927</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7</v>
+        <v>0.2755</v>
       </c>
       <c r="H15" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.8842</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6078</v>
+        <v>-0.6087</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1932</v>
+        <v>1.9499</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1559</v>
+        <v>1.6892</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0373</v>
+        <v>0.2607</v>
       </c>
       <c r="M15" t="n">
-        <v>0.5069</v>
+        <v>-1.6744</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0636</v>
+        <v>-0.805</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5705</v>
+        <v>-0.8694</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6805</v>
+        <v>0.9105</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6805</v>
+        <v>2.0487</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0916</v>
+        <v>-0.1639</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1391</v>
+        <v>-0.2978</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2308</v>
+        <v>0.1339</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3856</v>
+        <v>0.7739</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X15" t="n">
-        <v>0.3856</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="16">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2687</v>
+        <v>1.0864</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.189</v>
+        <v>-0.6636</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4577</v>
+        <v>1.7501</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1425</v>
+        <v>-0.1399</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3506</v>
+        <v>0.3531</v>
       </c>
       <c r="I16" t="n">
         <v>-0.4931</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.6971000000000001</v>
+        <v>-0.7007</v>
       </c>
       <c r="K16" t="n">
-        <v>0.052</v>
+        <v>0.0517</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5546</v>
+        <v>0.5608</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2986</v>
+        <v>0.3014</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2559</v>
+        <v>0.2593</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5039</v>
+        <v>0.3159</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5081</v>
+        <v>0.037</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0042</v>
+        <v>0.2788</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. WONG</t>
+          <t>M. TOBEY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6456</v>
+        <v>0.3867</v>
       </c>
       <c r="E17" t="n">
-        <v>3.0667</v>
+        <v>2.2024</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.4211</v>
+        <v>-1.8156</v>
       </c>
       <c r="G17" t="n">
-        <v>-4.2499</v>
+        <v>0.3615</v>
       </c>
       <c r="H17" t="n">
-        <v>-4.1512</v>
+        <v>0.7351</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.09859999999999999</v>
+        <v>-0.3737</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.1165</v>
+        <v>1.1319</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.5291</v>
+        <v>0.6927</v>
       </c>
       <c r="L17" t="n">
-        <v>1.4126</v>
+        <v>0.4392</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.1334</v>
+        <v>-0.7704</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.6221</v>
+        <v>0.0424</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.5113</v>
+        <v>-0.8129</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.2268</v>
+        <v>1.1382</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9073</v>
+        <v>1.1382</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7516</v>
+        <v>-0.0234</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9467</v>
+        <v>-0.019</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1951</v>
+        <v>-0.0044</v>
       </c>
       <c r="V17" t="n">
-        <v>4.3707</v>
+        <v>-1.0895</v>
       </c>
       <c r="W17" t="n">
-        <v>4.3707</v>
+        <v>1.0895</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Z. SAMAR</t>
+          <t>I. WONG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1617</v>
+        <v>0.0709</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.1788</v>
+        <v>2.3087</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0172</v>
+        <v>-2.2378</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2007</v>
+        <v>-4.2625</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6592</v>
+        <v>-4.1611</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4585</v>
+        <v>-0.1014</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0733</v>
+        <v>-1.1524</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.8943</v>
+        <v>-2.552</v>
       </c>
       <c r="L18" t="n">
-        <v>0.9675</v>
+        <v>1.3997</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.274</v>
+        <v>-3.1102</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2351</v>
+        <v>-1.6091</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.509</v>
+        <v>-1.5011</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="S18" t="n">
-        <v>0.039</v>
+        <v>0.2031</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1179</v>
+        <v>0.2413</v>
       </c>
       <c r="U18" t="n">
-        <v>0.157</v>
+        <v>-0.0381</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>4.3579</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>4.3579</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. TOBEY</t>
+          <t>Z. SAMAR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2397</v>
+        <v>-0.1003</v>
       </c>
       <c r="E19" t="n">
-        <v>1.9836</v>
+        <v>-1.3304</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.2233</v>
+        <v>1.23</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3545</v>
+        <v>-0.2106</v>
       </c>
       <c r="H19" t="n">
-        <v>0.733</v>
+        <v>-0.6741</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3785</v>
+        <v>0.4635</v>
       </c>
       <c r="J19" t="n">
-        <v>1.148</v>
+        <v>0.0427</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7029</v>
+        <v>-0.9177999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4451</v>
+        <v>0.9605</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7935</v>
+        <v>-0.2533</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0301</v>
+        <v>0.2437</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8236</v>
+        <v>-0.497</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1342</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6357</v>
+        <v>0.1103</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2571</v>
+        <v>-0.2349</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3787</v>
+        <v>0.3452</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.1853</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>K. KUATH</t>
+          <t>N. BRUSSINO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2142</v>
+        <v>-1.42</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7795</v>
+        <v>-3.2951</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4347</v>
+        <v>1.8751</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.2788</v>
+        <v>-3.069</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3912</v>
+        <v>0.7123</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8875999999999999</v>
+        <v>-3.7813</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1093</v>
+        <v>-2.1843</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0346</v>
+        <v>0.8856000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0746</v>
+        <v>-3.0699</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.388</v>
+        <v>-0.8847</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4258</v>
+        <v>-0.1733</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9622000000000001</v>
+        <v>-0.7114</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4537</v>
+        <v>2.5039</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4537</v>
+        <v>2.5039</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6179</v>
+        <v>-0.855</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2782</v>
+        <v>-1.1109</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3396</v>
+        <v>0.2559</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.7712</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.6105</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>N. BRUSSINO</t>
+          <t>K. KUATH</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4802</v>
+        <v>-1.7171</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.7198</v>
+        <v>-0.5492</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2395</v>
+        <v>-1.1679</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.0537</v>
+        <v>-1.2672</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7128</v>
+        <v>-0.3825</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.7665</v>
+        <v>-0.8847</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.138</v>
+        <v>0.1089</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9036</v>
+        <v>0.0345</v>
       </c>
       <c r="L21" t="n">
-        <v>-3.0416</v>
+        <v>0.0745</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9157</v>
+        <v>-1.3761</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1908</v>
+        <v>-0.4169</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.7249</v>
+        <v>-0.9592000000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>2.4952</v>
+        <v>0.4553</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.4952</v>
+        <v>0.4553</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.9217</v>
+        <v>-0.1312</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.5818</v>
+        <v>-0.0419</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.34</v>
+        <v>-0.0893</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.7739</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.6162</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.5704</v>
+        <v>-2.5067</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6936</v>
+        <v>0.5491</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.2641</v>
+        <v>-3.0558</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.4636</v>
+        <v>-1.4627</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4588</v>
+        <v>-0.4649</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.0048</v>
+        <v>-0.9977</v>
       </c>
       <c r="J22" t="n">
-        <v>0.199</v>
+        <v>0.1844</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1243</v>
+        <v>0.1099</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.6626</v>
+        <v>-1.6471</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5831</v>
+        <v>-0.5749</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.0795</v>
+        <v>-1.0722</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3883</v>
+        <v>0.4599</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5777</v>
+        <v>0.4621</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1893</v>
+        <v>-0.0022</v>
       </c>
       <c r="V22" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W22" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.5631</v>
+        <v>-3.1783</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.6537</v>
+        <v>-1.1095</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.9093</v>
+        <v>-2.0688</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.1568</v>
+        <v>-1.1606</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.3997</v>
+        <v>-0.3992</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.757</v>
+        <v>-0.7614</v>
       </c>
       <c r="J23" t="n">
-        <v>0.9426</v>
+        <v>0.9166</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0897</v>
+        <v>0.0755</v>
       </c>
       <c r="L23" t="n">
-        <v>0.8529</v>
+        <v>0.8411</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.0993</v>
+        <v>-2.0772</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4894</v>
+        <v>-0.4747</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.6099</v>
+        <v>-1.6025</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0058</v>
+        <v>0.3984</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6079</v>
+        <v>-0.0166</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6021</v>
+        <v>0.4149</v>
       </c>
       <c r="V23" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="W23" t="n">
-        <v>1.4141</v>
+        <v>1.405</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.0674</v>
+        <v>-3.5981</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.4831</v>
+        <v>-0.1423</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.5843</v>
+        <v>-3.4558</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.3072</v>
+        <v>-1.3004</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5453</v>
+        <v>0.5511</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.8525</v>
+        <v>-1.8515</v>
       </c>
       <c r="J24" t="n">
-        <v>0.4726</v>
+        <v>0.4597</v>
       </c>
       <c r="K24" t="n">
-        <v>0.8139</v>
+        <v>0.8101</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.3413</v>
+        <v>-0.3505</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.7798</v>
+        <v>-1.7601</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2685</v>
+        <v>-0.259</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.5113</v>
+        <v>-1.5011</v>
       </c>
       <c r="P24" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6163999999999999</v>
+        <v>-0.1674</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9557</v>
+        <v>-0.602</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3393</v>
+        <v>0.4345</v>
       </c>
       <c r="V24" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.3001</v>
+        <v>-5.2788</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.9036</v>
+        <v>-5.9432</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6035</v>
+        <v>0.6644</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.2367</v>
+        <v>-3.2446</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.9941</v>
+        <v>-2.9955</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2426</v>
+        <v>-0.2491</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.0323</v>
+        <v>-3.0609</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.0242</v>
+        <v>-3.0379</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.0081</v>
+        <v>-0.023</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.2044</v>
+        <v>-0.1836</v>
       </c>
       <c r="N25" t="n">
-        <v>0.0301</v>
+        <v>0.0424</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R25" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.2922</v>
+        <v>-0.2603</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.378</v>
+        <v>-0.3768</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0859</v>
+        <v>0.1165</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.3176</v>
+        <v>-1.3187</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.2249</v>
+        <v>-0.2292</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-14.6616</v>
+        <v>-12.288</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.7845</v>
+        <v>-6.0798</v>
       </c>
       <c r="F26" t="n">
-        <v>-8.877099999999999</v>
+        <v>-6.208</v>
       </c>
       <c r="G26" t="n">
-        <v>-14.7792</v>
+        <v>-14.7707</v>
       </c>
       <c r="H26" t="n">
-        <v>-5.743</v>
+        <v>-5.744100000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>-9.035899999999998</v>
+        <v>-9.026700000000002</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.8876</v>
+        <v>-2.111800000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.8737</v>
+        <v>-2.0034</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.01419999999999949</v>
+        <v>-0.1084000000000002</v>
       </c>
       <c r="M26" t="n">
-        <v>-12.8912</v>
+        <v>-12.6589</v>
       </c>
       <c r="N26" t="n">
-        <v>-3.8692</v>
+        <v>-3.7408</v>
       </c>
       <c r="O26" t="n">
-        <v>-9.022</v>
+        <v>-8.918300000000002</v>
       </c>
       <c r="P26" t="n">
-        <v>2.2684</v>
+        <v>2.2763</v>
       </c>
       <c r="Q26" t="n">
-        <v>-11.3417</v>
+        <v>-11.3817</v>
       </c>
       <c r="R26" t="n">
-        <v>13.6101</v>
+        <v>13.658</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.0869</v>
+        <v>0.2779</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.8749</v>
+        <v>-1.862</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.2118000000000001</v>
+        <v>2.1397</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.06430000000000113</v>
+        <v>-0.07150000000000012</v>
       </c>
       <c r="W26" t="n">
-        <v>9.3201</v>
+        <v>9.275399999999999</v>
       </c>
       <c r="X26" t="n">
-        <v>-9.3842</v>
+        <v>-9.3468</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104613_W18.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104613_W18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0.6162</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104613_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104613_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104613_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104613_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104613_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104613_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104613_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104613_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104613_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104613_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104613_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-9.275399999999999</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104613_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104613_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104613_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104613_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104613_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104613_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104613_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104613_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104613_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104613_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104613_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104613_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-9.3468</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
